--- a/data/trans_orig/P04B3_3_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_3_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su vivienda tiene goteras, humedades en paredes, suelos, techos o cimientos, o podredumbre en suelos, marcos de ventanas o puertas en 2023</t>
+          <t>Población según si su vivienda tiene goteras, humedades en paredes, suelos, techos o cimientos, o podredumbre en suelos, marcos de ventanas o puertas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>333</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19936</t>
+          <t>21035</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8497</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2257</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22743</t>
+          <t>24403</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11584</t>
+          <t>10780</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48654</t>
+          <t>48965</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18360</t>
+          <t>18117</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46565</t>
+          <t>45815</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34535</t>
+          <t>35369</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>79246</t>
+          <t>79065</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>344634</t>
+          <t>346946</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>384692</t>
+          <t>385435</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>262487</t>
+          <t>264120</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>292582</t>
+          <t>292569</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>621740</t>
+          <t>622995</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>671175</t>
+          <t>670123</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27370</t>
+          <t>27884</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2248</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>14091</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12158</t>
+          <t>12901</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>37787</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25626</t>
+          <t>23772</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55861</t>
+          <t>57293</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28155</t>
+          <t>28103</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63594</t>
+          <t>64175</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>61196</t>
+          <t>63483</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>109215</t>
+          <t>110159</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>350271</t>
+          <t>347803</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>384362</t>
+          <t>386269</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>441149</t>
+          <t>439629</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>480662</t>
+          <t>480570</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>803012</t>
+          <t>799388</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>857458</t>
+          <t>854057</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13295</t>
+          <t>14669</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,47 +1657,47 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>6603</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>3277</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>11788</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>6603</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2997</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>11371</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8029</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21845</t>
+          <t>20796</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38910</t>
+          <t>38874</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68529</t>
+          <t>67440</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24449</t>
+          <t>24960</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48118</t>
+          <t>46274</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68052</t>
+          <t>70086</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>104068</t>
+          <t>105940</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>459102</t>
+          <t>461445</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>490425</t>
+          <t>491391</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>536259</t>
+          <t>536529</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>560963</t>
+          <t>561253</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1007976</t>
+          <t>1007117</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1045737</t>
+          <t>1046673</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18832</t>
+          <t>18916</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11216</t>
+          <t>11651</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40520</t>
+          <t>38583</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15539</t>
+          <t>15514</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48497</t>
+          <t>47502</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14536</t>
+          <t>14819</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62515</t>
+          <t>61232</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47472</t>
+          <t>47123</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72538</t>
+          <t>72586</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56282</t>
+          <t>56906</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>126955</t>
+          <t>126223</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>810761</t>
+          <t>812266</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>868197</t>
+          <t>867343</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>613769</t>
+          <t>614369</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>648646</t>
+          <t>649773</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1437918</t>
+          <t>1437662</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1531870</t>
+          <t>1523415</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14684</t>
+          <t>14894</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7208</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18194</t>
+          <t>17813</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>13862</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28538</t>
+          <t>28630</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31836</t>
+          <t>31659</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>54916</t>
+          <t>54865</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36752</t>
+          <t>36341</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>55853</t>
+          <t>56407</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>72823</t>
+          <t>73170</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>104017</t>
+          <t>104021</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>497293</t>
+          <t>496477</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>521847</t>
+          <t>522112</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>479076</t>
+          <t>477722</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>500183</t>
+          <t>500003</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>983097</t>
+          <t>983460</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1017441</t>
+          <t>1017237</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,76%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>893</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13589</t>
+          <t>13495</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>25781</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42803</t>
+          <t>44406</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35875</t>
+          <t>36025</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>449633</t>
+          <t>457050</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72377</t>
+          <t>71952</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>637431</t>
+          <t>593796</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>60,84%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>320952</t>
+          <t>319683</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>339145</t>
+          <t>339057</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>156816</t>
+          <t>149007</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>566335</t>
+          <t>566018</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>333651</t>
+          <t>378475</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>893467</t>
+          <t>893835</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,59%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>975</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6398</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,47 +3516,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>5858</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>3263</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>10656</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>1,5%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>5858</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>3245</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>10103</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17179</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31376</t>
+          <t>31535</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>31576</t>
+          <t>31652</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>49155</t>
+          <t>48525</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>52089</t>
+          <t>51871</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>74588</t>
+          <t>74573</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>248969</t>
+          <t>248182</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>263849</t>
+          <t>263498</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>373435</t>
+          <t>373816</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>391676</t>
+          <t>391107</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>650871</t>
+          <t>651145</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,89%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>37661</t>
+          <t>36415</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>73256</t>
+          <t>72470</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>39789</t>
+          <t>39343</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>76178</t>
+          <t>74477</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>85746</t>
+          <t>83956</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>133233</t>
+          <t>132048</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>199841</t>
+          <t>196839</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>293535</t>
+          <t>290678</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>290415</t>
+          <t>286061</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1168481</t>
+          <t>1100430</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>531560</t>
+          <t>533205</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1493205</t>
+          <t>1399155</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3107973</t>
+          <t>3110816</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3219287</t>
+          <t>3222062</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2494813</t>
+          <t>2564264</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3364277</t>
+          <t>3366754</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5594783</t>
+          <t>5702669</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6533290</t>
+          <t>6531483</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B3_3_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_3_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21035</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>12505</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>4093</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24403</t>
+          <t>24577</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24233</t>
+          <t>26595</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10780</t>
+          <t>12187</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48965</t>
+          <t>45517</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30055</t>
+          <t>39661</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18117</t>
+          <t>25319</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45815</t>
+          <t>58491</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>54288</t>
+          <t>66256</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35369</t>
+          <t>45812</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>79065</t>
+          <t>94973</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>370174</t>
+          <t>374851</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>346946</t>
+          <t>354681</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>385435</t>
+          <t>391723</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>280512</t>
+          <t>318531</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>264120</t>
+          <t>299841</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>292569</t>
+          <t>333313</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>650686</t>
+          <t>693383</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>622995</t>
+          <t>663425</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>670123</t>
+          <t>714264</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15790</t>
+          <t>18138</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27884</t>
+          <t>32102</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2248</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14091</t>
+          <t>17292</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>22259</t>
+          <t>25836</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12901</t>
+          <t>15668</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37787</t>
+          <t>42703</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38500</t>
+          <t>41970</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23772</t>
+          <t>28389</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57293</t>
+          <t>62552</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47296</t>
+          <t>57266</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28103</t>
+          <t>42701</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>64175</t>
+          <t>73263</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>85796</t>
+          <t>99237</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>63483</t>
+          <t>79497</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>110159</t>
+          <t>122104</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>369257</t>
+          <t>416781</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>347803</t>
+          <t>395742</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>386269</t>
+          <t>433121</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>458328</t>
+          <t>436769</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>439629</t>
+          <t>420642</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>480570</t>
+          <t>452280</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>827585</t>
+          <t>853550</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>799388</t>
+          <t>829206</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>854057</t>
+          <t>878111</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6652</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2791</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14669</t>
+          <t>16927</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>8982</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11788</t>
+          <t>16226</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>13254</t>
+          <t>17646</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>10706</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20796</t>
+          <t>26316</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>65371</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38874</t>
+          <t>49532</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67440</t>
+          <t>81946</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35271</t>
+          <t>40720</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24960</t>
+          <t>31258</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46274</t>
+          <t>51950</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>87781</t>
+          <t>106091</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70086</t>
+          <t>90671</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105940</t>
+          <t>126919</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>477012</t>
+          <t>545623</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>461445</t>
+          <t>529219</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>491391</t>
+          <t>562659</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>549237</t>
+          <t>571776</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>536529</t>
+          <t>559904</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>561253</t>
+          <t>582475</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1026248</t>
+          <t>1117399</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1007117</t>
+          <t>1094444</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1046673</t>
+          <t>1134945</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>591111</t>
+          <t>621478</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>591111</t>
+          <t>621478</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>591111</t>
+          <t>621478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1127284</t>
+          <t>1241137</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1127284</t>
+          <t>1241137</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1127284</t>
+          <t>1241137</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18916</t>
+          <t>19700</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19497</t>
+          <t>16073</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11651</t>
+          <t>10357</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38583</t>
+          <t>23385</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>28761</t>
+          <t>26672</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15514</t>
+          <t>18322</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47502</t>
+          <t>38018</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>39734</t>
+          <t>47583</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14819</t>
+          <t>35738</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61232</t>
+          <t>63316</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>59166</t>
+          <t>64988</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47123</t>
+          <t>54534</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72586</t>
+          <t>79426</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>98900</t>
+          <t>112571</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56906</t>
+          <t>93661</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>126223</t>
+          <t>130707</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>837784</t>
+          <t>641501</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>812266</t>
+          <t>625624</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>867343</t>
+          <t>654409</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>633483</t>
+          <t>655121</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>614369</t>
+          <t>640406</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>649773</t>
+          <t>667759</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1471266</t>
+          <t>1296622</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1437662</t>
+          <t>1275054</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1523415</t>
+          <t>1315366</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>886782</t>
+          <t>699683</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>886782</t>
+          <t>699683</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>886782</t>
+          <t>699683</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>712146</t>
+          <t>736182</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>712146</t>
+          <t>736182</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>712146</t>
+          <t>736182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1598927</t>
+          <t>1435865</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1598927</t>
+          <t>1435865</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1598927</t>
+          <t>1435865</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>9294</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>5155</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14894</t>
+          <t>15863</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,22 +2584,22 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11650</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7382</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17813</t>
+          <t>20273</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>20082</t>
+          <t>22909</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13862</t>
+          <t>15577</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28630</t>
+          <t>31858</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42188</t>
+          <t>45989</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31659</t>
+          <t>34657</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>54865</t>
+          <t>60445</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>45834</t>
+          <t>52836</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36341</t>
+          <t>42128</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56407</t>
+          <t>64580</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>88021</t>
+          <t>98825</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73170</t>
+          <t>81606</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>104021</t>
+          <t>117406</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>510614</t>
+          <t>554063</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>496477</t>
+          <t>539085</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>522112</t>
+          <t>566707</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>489809</t>
+          <t>541720</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>477722</t>
+          <t>529557</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>500003</t>
+          <t>554087</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1000423</t>
+          <t>1095783</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>983460</t>
+          <t>1076252</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1017237</t>
+          <t>1113695</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>547293</t>
+          <t>608170</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>547293</t>
+          <t>608170</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>547293</t>
+          <t>608170</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1108526</t>
+          <t>1217517</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1108526</t>
+          <t>1217517</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1108526</t>
+          <t>1217517</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>8058</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13495</t>
+          <t>15295</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>33684</t>
+          <t>38947</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25781</t>
+          <t>29718</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44406</t>
+          <t>50459</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>231265</t>
+          <t>29624</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36025</t>
+          <t>23168</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>457050</t>
+          <t>38194</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>264950</t>
+          <t>68570</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>71952</t>
+          <t>56141</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>593796</t>
+          <t>82189</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>330109</t>
+          <t>363240</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>319683</t>
+          <t>351644</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>339057</t>
+          <t>373252</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>372840</t>
+          <t>404903</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>149007</t>
+          <t>396044</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>566018</t>
+          <t>411936</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>702950</t>
+          <t>768142</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>378475</t>
+          <t>753659</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>893835</t>
+          <t>781115</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>92,37%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>607792</t>
+          <t>438570</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>607792</t>
+          <t>438570</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>607792</t>
+          <t>438570</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>975958</t>
+          <t>845649</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>975958</t>
+          <t>845649</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>975958</t>
+          <t>845649</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,22 +3531,22 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>5858</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10776</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -3574,22 +3574,22 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>23211</t>
+          <t>25763</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>18296</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31535</t>
+          <t>33913</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>38935</t>
+          <t>42811</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>31652</t>
+          <t>33739</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>48525</t>
+          <t>53235</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>62145</t>
+          <t>68574</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>51871</t>
+          <t>56994</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>74573</t>
+          <t>82666</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>256740</t>
+          <t>281416</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>248182</t>
+          <t>272442</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>263498</t>
+          <t>289042</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>383847</t>
+          <t>418240</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>373816</t>
+          <t>407980</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>391107</t>
+          <t>427617</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>640587</t>
+          <t>699656</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>628139</t>
+          <t>685506</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>651145</t>
+          <t>711386</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,81%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>52898</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>36415</t>
+          <t>45821</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>72470</t>
+          <t>79609</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>53587</t>
+          <t>58289</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>39343</t>
+          <t>46237</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>74477</t>
+          <t>72479</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>106485</t>
+          <t>119243</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>83956</t>
+          <t>98452</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>132048</t>
+          <t>142678</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>254060</t>
+          <t>292218</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>196839</t>
+          <t>258210</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>290678</t>
+          <t>326608</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>487822</t>
+          <t>327905</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>286061</t>
+          <t>296155</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1100430</t>
+          <t>364719</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>741882</t>
+          <t>620124</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>533205</t>
+          <t>576867</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1399155</t>
+          <t>675168</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>3151690</t>
+          <t>3177477</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3110816</t>
+          <t>3135900</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3222062</t>
+          <t>3212229</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>3168056</t>
+          <t>3347059</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2564264</t>
+          <t>3309386</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3366754</t>
+          <t>3379735</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>6319746</t>
+          <t>6524536</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5702669</t>
+          <t>6465687</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6531483</t>
+          <t>6576337</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3458648</t>
+          <t>3530650</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3458648</t>
+          <t>3530650</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3458648</t>
+          <t>3530650</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3709465</t>
+          <t>3733253</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3709465</t>
+          <t>3733253</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3709465</t>
+          <t>3733253</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7168113</t>
+          <t>7263903</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7168113</t>
+          <t>7263903</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7168113</t>
+          <t>7263903</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
